--- a/SapAriba_Elanco_performer/lib/net45/Data/Config.xlsx
+++ b/SapAriba_Elanco_performer/lib/net45/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\Elanco process\SapAriba_Elanco_performer\lib\net45\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1UiPath\NA-Automation\USA-Elanco\SapAriba_Elanco_performer\lib\net45\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{328B1EC5-ADD4-4A46-8E91-D6A67DC41A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5D8DAE-A0D4-4F56-95E1-7152AE8F2151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20700" windowHeight="8745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -346,18 +346,9 @@
     <t>Pre-requiste Script for Logging to Chrome in Incognitive Mode</t>
   </si>
   <si>
-    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\AR_Folder\Downloaded Files\</t>
-  </si>
-  <si>
-    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\AR_Folder\Exceptions_Screenshots</t>
-  </si>
-  <si>
     <t>NoSentMail</t>
   </si>
   <si>
-    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\grm-usa-ar-ariba-Performer\Chrome_Configuration\1files\1files\chrome-profiles\bot</t>
-  </si>
-  <si>
     <t>USARegion</t>
   </si>
   <si>
@@ -409,15 +400,6 @@
     <t>GMUSA_AR_Mars_Credentials</t>
   </si>
   <si>
-    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\AR_Folder\Elanco_PDF</t>
-  </si>
-  <si>
-    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\AR_Folder\ElancoExecutionReport\PreparationElancoExecutionReport\</t>
-  </si>
-  <si>
-    <t>C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Documents\AR_Folder\Template_Files\elancoTrackerTemplate.xlsx</t>
-  </si>
-  <si>
     <t>It takes from Asset Elanco_Queue_Name as below</t>
   </si>
   <si>
@@ -461,6 +443,24 @@
   </si>
   <si>
     <t>SharepointPath</t>
+  </si>
+  <si>
+    <t>C:\Users\grmusarpadev17\OneDrive - insidemedia.net\Documents\AR_Folder\Template_Files\elancoTrackerTemplate.xlsx</t>
+  </si>
+  <si>
+    <t>C:\Users\grmusarpadev17\OneDrive - insidemedia.net\Documents\AR_Folder\Downloaded Files\</t>
+  </si>
+  <si>
+    <t>C:\Users\grmusarpadev17\OneDrive - insidemedia.net\Documents\AR_Folder\Elanco_PDF</t>
+  </si>
+  <si>
+    <t>C:\Users\grmusarpadev17\OneDrive - insidemedia.net\Documents\AR_Folder\ElancoExecutionReport\PreparationElancoExecutionReport\</t>
+  </si>
+  <si>
+    <t>C:\Users\grmusarpadev17\OneDrive - insidemedia.net\Documents\grm-usa-ar-ariba-Performer\Chrome_Configuration\1files\1files\chrome-profiles\bot</t>
+  </si>
+  <si>
+    <t>C:\Users\grmusarpadev17\OneDrive - insidemedia.net\Documents\AR_Folder\Exceptions_Screenshots</t>
   </si>
 </sst>
 </file>
@@ -1445,7 +1445,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>21</v>
@@ -1472,7 +1472,7 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B5" s="2" t="b">
         <v>1</v>
@@ -1508,7 +1508,7 @@
         <v>55</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>56</v>
@@ -1519,7 +1519,7 @@
         <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>58</v>
@@ -1527,10 +1527,10 @@
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2"/>
     </row>
@@ -1539,18 +1539,18 @@
         <v>65</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
@@ -1569,7 +1569,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>101</v>
@@ -1580,15 +1580,15 @@
         <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1">
@@ -1596,42 +1596,42 @@
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1">
       <c r="A23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.25" customHeight="1">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.25" customHeight="1"/>
@@ -2676,7 +2676,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -2769,18 +2769,18 @@
     </row>
     <row r="16" spans="1:26" ht="16.899999999999999" customHeight="1">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1"/>
@@ -3814,7 +3814,7 @@
         <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
         <v>31</v>
@@ -3836,7 +3836,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1">
@@ -3889,10 +3889,10 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
       <c r="A11" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
         <v>80</v>
@@ -3900,10 +3900,10 @@
     </row>
     <row r="12" spans="1:26" ht="14.25" customHeight="1">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D12" t="s">
         <v>81</v>
@@ -3933,16 +3933,16 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>85</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
@@ -3979,10 +3979,10 @@
     </row>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1"/>
@@ -5178,6 +5178,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
+    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045A9A53AB2AD7C409EFC96CC55961B83" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9ff56ad652d5e5faec097a6229aaa81f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="649a79cd-06e4-47a3-aac9-21cb806f3675" xmlns:ns3="7f25b792-b2ba-4b5c-8669-b39a27555406" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3487cd39016dc6f53b8dc1d1dd8e1aa7" ns2:_="" ns3:_="">
     <xsd:import namespace="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
@@ -5412,28 +5433,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A4EFC28-1971-4E7F-9692-160FEFF36FBB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
+    <ds:schemaRef ds:uri="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
+    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
+    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
-    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18138064-1949-4AB1-8912-B181F8257E43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D1853F4-B683-45EB-930B-C52788084F76}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5450,25 +5471,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18138064-1949-4AB1-8912-B181F8257E43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A4EFC28-1971-4E7F-9692-160FEFF36FBB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c4012d6b-a91c-4ec0-90d0-0537ad76586d"/>
-    <ds:schemaRef ds:uri="ef49ae6b-e58c-46b9-9be1-3da75242d3af"/>
-    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
-    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>